--- a/xlsx/carteira_mensal/Jan_2026.xlsx
+++ b/xlsx/carteira_mensal/Jan_2026.xlsx
@@ -1110,7 +1110,7 @@
         <v>49</v>
       </c>
       <c r="F40" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G40" t="s">
         <v>50</v>

--- a/xlsx/carteira_mensal/Jan_2026.xlsx
+++ b/xlsx/carteira_mensal/Jan_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="117">
   <si>
     <t>Acompanhamento de Carteira</t>
   </si>
@@ -75,24 +75,24 @@
     <t>Data de Criação do Projeto</t>
   </si>
   <si>
+    <t>/  /     até   /  /</t>
+  </si>
+  <si>
+    <t>Data de Criação do Orçamento</t>
+  </si>
+  <si>
+    <t>/  /     00:00 até   /  /     00:00</t>
+  </si>
+  <si>
+    <t>Data de Criação do Contrato</t>
+  </si>
+  <si>
+    <t>Data de Assinatura do Contrato</t>
+  </si>
+  <si>
     <t>01/01/2026 até 31/01/2026</t>
   </si>
   <si>
-    <t>Data de Criação do Orçamento</t>
-  </si>
-  <si>
-    <t>/  /     00:00 até   /  /     00:00</t>
-  </si>
-  <si>
-    <t>Data de Criação do Contrato</t>
-  </si>
-  <si>
-    <t>/  /     até   /  /</t>
-  </si>
-  <si>
-    <t>Data de Assinatura do Contrato</t>
-  </si>
-  <si>
     <t>Data de Criação do Cliente</t>
   </si>
   <si>
@@ -153,6 +153,36 @@
     <t>Contrato</t>
   </si>
   <si>
+    <t>Maria Beatriz Ribeiro de Andrade</t>
+  </si>
+  <si>
+    <t>Porta</t>
+  </si>
+  <si>
+    <t>15/12/25</t>
+  </si>
+  <si>
+    <t>ERIC SERPA</t>
+  </si>
+  <si>
+    <t>Orçamento 1</t>
+  </si>
+  <si>
+    <t>10/01/26</t>
+  </si>
+  <si>
+    <t>LUANNA CANUTO RODRIGUES</t>
+  </si>
+  <si>
+    <t>20/12/25</t>
+  </si>
+  <si>
+    <t>BIANCA RODRIGUES</t>
+  </si>
+  <si>
+    <t>08/01/26</t>
+  </si>
+  <si>
     <t>Rafaella Guelman</t>
   </si>
   <si>
@@ -165,9 +195,6 @@
     <t>ROSANGELA PACHECO</t>
   </si>
   <si>
-    <t>Orçamento 1</t>
-  </si>
-  <si>
     <t>13/01/26</t>
   </si>
   <si>
@@ -180,24 +207,15 @@
     <t>06/01/26</t>
   </si>
   <si>
-    <t>ERIC SERPA</t>
-  </si>
-  <si>
     <t>27/01/26</t>
   </si>
   <si>
     <t>Anastacia Cristina Torres Coelho</t>
   </si>
   <si>
-    <t>Porta</t>
-  </si>
-  <si>
     <t>07/01/26</t>
   </si>
   <si>
-    <t>BIANCA RODRIGUES</t>
-  </si>
-  <si>
     <t>09/01/26</t>
   </si>
   <si>
@@ -207,12 +225,6 @@
     <t>Google</t>
   </si>
   <si>
-    <t>08/01/26</t>
-  </si>
-  <si>
-    <t>10/01/26</t>
-  </si>
-  <si>
     <t>Angelo José Valcácio Filho</t>
   </si>
   <si>
@@ -309,7 +321,7 @@
     <t>Quantidade de Projetos</t>
   </si>
   <si>
-    <t>18</t>
+    <t>20</t>
   </si>
   <si>
     <t>Quantidade de Orçamentos</t>
@@ -318,40 +330,40 @@
     <t>Pontuação Total</t>
   </si>
   <si>
-    <t>1.92</t>
+    <t>1.91</t>
   </si>
   <si>
     <t>Valor Total Bruto</t>
   </si>
   <si>
-    <t>522.166,81</t>
-  </si>
-  <si>
-    <t>397.881,12</t>
+    <t>598.295,02</t>
+  </si>
+  <si>
+    <t>447.440,41</t>
   </si>
   <si>
     <t>Valor Total Líquido</t>
   </si>
   <si>
-    <t>342.521,40</t>
+    <t>389.769,44</t>
   </si>
   <si>
     <t>Total Líquido sem o Per</t>
   </si>
   <si>
-    <t>341.604,89</t>
+    <t>388.852,93</t>
   </si>
   <si>
     <t>Total Diferença Financeira</t>
   </si>
   <si>
-    <t>55.359,72</t>
+    <t>57.670,97</t>
   </si>
   <si>
     <t>Total Adicional dos Ambientes</t>
   </si>
   <si>
-    <t>22.165,34</t>
+    <t>24.409,43</t>
   </si>
 </sst>
 </file>
@@ -420,7 +432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:O59"/>
+  <dimension ref="A2:O61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="53.22265625" customWidth="true" bestFit="true"/>
@@ -548,15 +560,15 @@
         <v>23</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -564,7 +576,7 @@
         <v>26</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -572,7 +584,7 @@
         <v>27</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -678,7 +690,7 @@
         <v>47</v>
       </c>
       <c r="C31" t="n">
-        <v>526.0</v>
+        <v>511.0</v>
       </c>
       <c r="D31" t="s">
         <v>48</v>
@@ -696,22 +708,22 @@
         <v>51</v>
       </c>
       <c r="I31" t="n">
-        <v>13150.0</v>
+        <v>17032.0</v>
       </c>
       <c r="J31" t="n">
-        <v>482.51</v>
+        <v>1117.74</v>
       </c>
       <c r="K31" t="n">
-        <v>12667.49</v>
+        <v>15914.26</v>
       </c>
       <c r="L31" t="n">
-        <v>12667.49</v>
+        <v>15914.26</v>
       </c>
       <c r="M31" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="N31" t="n">
-        <v>52601.0</v>
+        <v>51101.0</v>
       </c>
       <c r="O31" t="s">
         <v>51</v>
@@ -722,16 +734,16 @@
         <v>52</v>
       </c>
       <c r="B32" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32" t="n">
+        <v>522.0</v>
+      </c>
+      <c r="D32" t="s">
         <v>53</v>
       </c>
-      <c r="C32" t="n">
-        <v>528.0</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>54</v>
-      </c>
-      <c r="E32" t="s">
-        <v>55</v>
       </c>
       <c r="F32" t="n">
         <v>1.0</v>
@@ -740,45 +752,45 @@
         <v>50</v>
       </c>
       <c r="H32" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I32" t="n">
-        <v>5145.0</v>
+        <v>32527.29</v>
       </c>
       <c r="J32" t="n">
-        <v>554.12</v>
+        <v>1193.51</v>
       </c>
       <c r="K32" t="n">
-        <v>4590.88</v>
+        <v>31333.78</v>
       </c>
       <c r="L32" t="n">
-        <v>4590.88</v>
+        <v>31333.78</v>
       </c>
       <c r="M32" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="N32" t="n">
-        <v>52801.0</v>
+        <v>52201.0</v>
       </c>
       <c r="O32" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" t="s">
         <v>57</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="n">
+        <v>526.0</v>
+      </c>
+      <c r="D33" t="s">
         <v>58</v>
       </c>
-      <c r="C33" t="n">
-        <v>532.0</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>59</v>
-      </c>
-      <c r="E33" t="s">
-        <v>60</v>
       </c>
       <c r="F33" t="n">
         <v>1.0</v>
@@ -787,92 +799,92 @@
         <v>50</v>
       </c>
       <c r="H33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I33" t="n">
-        <v>20700.0</v>
+        <v>13150.0</v>
       </c>
       <c r="J33" t="n">
-        <v>2168.77</v>
+        <v>482.51</v>
       </c>
       <c r="K33" t="n">
-        <v>18531.23</v>
+        <v>12667.49</v>
       </c>
       <c r="L33" t="n">
-        <v>18531.23</v>
+        <v>12667.49</v>
       </c>
       <c r="M33" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="N33" t="n">
-        <v>53201.0</v>
+        <v>52601.0</v>
       </c>
       <c r="O33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34" t="s">
         <v>62</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="n">
+        <v>528.0</v>
+      </c>
+      <c r="D34" t="s">
         <v>63</v>
-      </c>
-      <c r="C34" t="n">
-        <v>535.0</v>
-      </c>
-      <c r="D34" t="s">
-        <v>64</v>
       </c>
       <c r="E34" t="s">
         <v>49</v>
       </c>
       <c r="F34" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G34" t="s">
         <v>50</v>
       </c>
       <c r="H34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I34" t="n">
-        <v>8000.0</v>
+        <v>5145.0</v>
       </c>
       <c r="J34" t="n">
-        <v>293.54</v>
+        <v>554.12</v>
       </c>
       <c r="K34" t="n">
-        <v>7706.46</v>
+        <v>4590.88</v>
       </c>
       <c r="L34" t="n">
-        <v>7706.46</v>
+        <v>4590.88</v>
       </c>
       <c r="M34" t="n">
-        <v>2.99</v>
+        <v>1.9</v>
       </c>
       <c r="N34" t="n">
-        <v>53501.0</v>
+        <v>52801.0</v>
       </c>
       <c r="O34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>65</v>
+      </c>
+      <c r="B35" t="s">
+        <v>47</v>
+      </c>
+      <c r="C35" t="n">
+        <v>532.0</v>
+      </c>
+      <c r="D35" t="s">
         <v>66</v>
       </c>
-      <c r="B35" t="s">
-        <v>53</v>
-      </c>
-      <c r="C35" t="n">
-        <v>539.0</v>
-      </c>
-      <c r="D35" t="s">
-        <v>61</v>
-      </c>
       <c r="E35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F35" t="n">
         <v>1.0</v>
@@ -881,75 +893,75 @@
         <v>50</v>
       </c>
       <c r="H35" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I35" t="n">
-        <v>3578.79</v>
+        <v>20700.0</v>
       </c>
       <c r="J35" t="n">
-        <v>635.46</v>
+        <v>2168.77</v>
       </c>
       <c r="K35" t="n">
-        <v>2943.33</v>
+        <v>18531.23</v>
       </c>
       <c r="L35" t="n">
-        <v>2943.33</v>
+        <v>18531.23</v>
       </c>
       <c r="M35" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="N35" t="n">
-        <v>53901.0</v>
+        <v>53201.0</v>
       </c>
       <c r="O35" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B36" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C36" t="n">
-        <v>544.0</v>
+        <v>535.0</v>
       </c>
       <c r="D36" t="s">
+        <v>55</v>
+      </c>
+      <c r="E36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G36" t="s">
+        <v>50</v>
+      </c>
+      <c r="H36" t="s">
         <v>51</v>
       </c>
-      <c r="E36" t="s">
-        <v>55</v>
-      </c>
-      <c r="F36" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="G36" t="s">
-        <v>50</v>
-      </c>
-      <c r="H36" t="s">
-        <v>69</v>
-      </c>
       <c r="I36" t="n">
-        <v>27250.23</v>
+        <v>8000.0</v>
       </c>
       <c r="J36" t="n">
-        <v>2611.76</v>
+        <v>293.54</v>
       </c>
       <c r="K36" t="n">
-        <v>24638.47</v>
+        <v>7706.46</v>
       </c>
       <c r="L36" t="n">
-        <v>24638.47</v>
+        <v>7706.46</v>
       </c>
       <c r="M36" t="n">
-        <v>1.9</v>
+        <v>2.99</v>
       </c>
       <c r="N36" t="n">
-        <v>54401.0</v>
+        <v>53501.0</v>
       </c>
       <c r="O36" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37">
@@ -957,16 +969,16 @@
         <v>70</v>
       </c>
       <c r="B37" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C37" t="n">
-        <v>555.0</v>
+        <v>539.0</v>
       </c>
       <c r="D37" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E37" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F37" t="n">
         <v>1.0</v>
@@ -975,89 +987,89 @@
         <v>50</v>
       </c>
       <c r="H37" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="I37" t="n">
-        <v>25990.0</v>
+        <v>3578.79</v>
       </c>
       <c r="J37" t="n">
-        <v>969.71</v>
+        <v>635.46</v>
       </c>
       <c r="K37" t="n">
-        <v>25020.29</v>
+        <v>2943.33</v>
       </c>
       <c r="L37" t="n">
-        <v>25020.29</v>
+        <v>2943.33</v>
       </c>
       <c r="M37" t="n">
         <v>1.9</v>
       </c>
       <c r="N37" t="n">
-        <v>55501.0</v>
+        <v>53901.0</v>
       </c>
       <c r="O37" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>71</v>
+      </c>
+      <c r="B38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" t="n">
+        <v>544.0</v>
+      </c>
+      <c r="D38" t="s">
+        <v>60</v>
+      </c>
+      <c r="E38" t="s">
+        <v>49</v>
+      </c>
+      <c r="F38" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G38" t="s">
+        <v>50</v>
+      </c>
+      <c r="H38" t="s">
         <v>73</v>
       </c>
-      <c r="B38" t="s">
-        <v>68</v>
-      </c>
-      <c r="C38" t="n">
-        <v>554.0</v>
-      </c>
-      <c r="D38" t="s">
-        <v>71</v>
-      </c>
-      <c r="E38" t="s">
-        <v>60</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G38" t="s">
-        <v>50</v>
-      </c>
-      <c r="H38" t="s">
-        <v>74</v>
-      </c>
       <c r="I38" t="n">
-        <v>27006.0</v>
+        <v>27250.23</v>
       </c>
       <c r="J38" t="n">
-        <v>5120.3</v>
+        <v>2611.76</v>
       </c>
       <c r="K38" t="n">
-        <v>21885.7</v>
+        <v>24638.47</v>
       </c>
       <c r="L38" t="n">
-        <v>21885.7</v>
+        <v>24638.47</v>
       </c>
       <c r="M38" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="N38" t="n">
-        <v>55401.0</v>
+        <v>54401.0</v>
       </c>
       <c r="O38" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>74</v>
+      </c>
+      <c r="B39" t="s">
+        <v>47</v>
+      </c>
+      <c r="C39" t="n">
+        <v>555.0</v>
+      </c>
+      <c r="D39" t="s">
         <v>75</v>
-      </c>
-      <c r="B39" t="s">
-        <v>76</v>
-      </c>
-      <c r="C39" t="n">
-        <v>553.0</v>
-      </c>
-      <c r="D39" t="s">
-        <v>71</v>
       </c>
       <c r="E39" t="s">
         <v>49</v>
@@ -1069,28 +1081,28 @@
         <v>50</v>
       </c>
       <c r="H39" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I39" t="n">
-        <v>24000.0</v>
+        <v>25990.0</v>
       </c>
       <c r="J39" t="n">
-        <v>6656.96</v>
+        <v>969.71</v>
       </c>
       <c r="K39" t="n">
-        <v>17343.04</v>
+        <v>25020.29</v>
       </c>
       <c r="L39" t="n">
-        <v>16925.73</v>
+        <v>25020.29</v>
       </c>
       <c r="M39" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="N39" t="n">
-        <v>55301.0</v>
+        <v>55501.0</v>
       </c>
       <c r="O39" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40">
@@ -1098,63 +1110,63 @@
         <v>77</v>
       </c>
       <c r="B40" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C40" t="n">
-        <v>561.0</v>
+        <v>554.0</v>
       </c>
       <c r="D40" t="s">
+        <v>75</v>
+      </c>
+      <c r="E40" t="s">
+        <v>54</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G40" t="s">
+        <v>50</v>
+      </c>
+      <c r="H40" t="s">
         <v>78</v>
       </c>
-      <c r="E40" t="s">
-        <v>49</v>
-      </c>
-      <c r="F40" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="G40" t="s">
-        <v>50</v>
-      </c>
-      <c r="H40" t="s">
-        <v>79</v>
-      </c>
       <c r="I40" t="n">
-        <v>25333.58</v>
+        <v>27006.0</v>
       </c>
       <c r="J40" t="n">
-        <v>4217.18</v>
+        <v>5120.3</v>
       </c>
       <c r="K40" t="n">
-        <v>21116.4</v>
+        <v>21885.7</v>
       </c>
       <c r="L40" t="n">
-        <v>20617.2</v>
+        <v>21885.7</v>
       </c>
       <c r="M40" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="N40" t="n">
-        <v>56101.0</v>
+        <v>55401.0</v>
       </c>
       <c r="O40" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>79</v>
+      </c>
+      <c r="B41" t="s">
         <v>80</v>
       </c>
-      <c r="B41" t="s">
-        <v>47</v>
-      </c>
       <c r="C41" t="n">
-        <v>565.0</v>
+        <v>553.0</v>
       </c>
       <c r="D41" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E41" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F41" t="n">
         <v>1.0</v>
@@ -1163,139 +1175,139 @@
         <v>50</v>
       </c>
       <c r="H41" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I41" t="n">
-        <v>272.04</v>
+        <v>24000.0</v>
       </c>
       <c r="J41" t="n">
-        <v>0.0</v>
+        <v>6656.96</v>
       </c>
       <c r="K41" t="n">
-        <v>272.04</v>
+        <v>17343.04</v>
       </c>
       <c r="L41" t="n">
-        <v>272.04</v>
+        <v>16925.73</v>
       </c>
       <c r="M41" t="n">
-        <v>2.31</v>
+        <v>1.94</v>
       </c>
       <c r="N41" t="n">
-        <v>56501.0</v>
+        <v>55301.0</v>
       </c>
       <c r="O41" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>81</v>
+      </c>
+      <c r="B42" t="s">
+        <v>69</v>
+      </c>
+      <c r="C42" t="n">
+        <v>561.0</v>
+      </c>
+      <c r="D42" t="s">
         <v>82</v>
       </c>
-      <c r="B42" t="s">
-        <v>47</v>
-      </c>
-      <c r="C42" t="n">
-        <v>569.0</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
+        <v>59</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G42" t="s">
+        <v>50</v>
+      </c>
+      <c r="H42" t="s">
         <v>83</v>
       </c>
-      <c r="E42" t="s">
-        <v>60</v>
-      </c>
-      <c r="F42" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G42" t="s">
-        <v>50</v>
-      </c>
-      <c r="H42" t="s">
-        <v>84</v>
-      </c>
       <c r="I42" t="n">
-        <v>12268.1</v>
+        <v>25333.58</v>
       </c>
       <c r="J42" t="n">
-        <v>3175.81</v>
+        <v>4217.18</v>
       </c>
       <c r="K42" t="n">
-        <v>9092.29</v>
+        <v>21116.4</v>
       </c>
       <c r="L42" t="n">
-        <v>9092.29</v>
+        <v>20617.2</v>
       </c>
       <c r="M42" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="N42" t="n">
-        <v>56901.0</v>
+        <v>56101.0</v>
       </c>
       <c r="O42" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
+        <v>84</v>
+      </c>
+      <c r="B43" t="s">
+        <v>57</v>
+      </c>
+      <c r="C43" t="n">
+        <v>565.0</v>
+      </c>
+      <c r="D43" t="s">
         <v>85</v>
-      </c>
-      <c r="B43" t="s">
-        <v>63</v>
-      </c>
-      <c r="C43" t="n">
-        <v>568.0</v>
-      </c>
-      <c r="D43" t="s">
-        <v>83</v>
       </c>
       <c r="E43" t="s">
         <v>49</v>
       </c>
       <c r="F43" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G43" t="s">
         <v>50</v>
       </c>
       <c r="H43" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I43" t="n">
-        <v>50200.0</v>
+        <v>272.04</v>
       </c>
       <c r="J43" t="n">
-        <v>6551.57</v>
+        <v>0.0</v>
       </c>
       <c r="K43" t="n">
-        <v>43648.43</v>
+        <v>272.04</v>
       </c>
       <c r="L43" t="n">
-        <v>43648.43</v>
+        <v>272.04</v>
       </c>
       <c r="M43" t="n">
-        <v>1.9</v>
+        <v>2.31</v>
       </c>
       <c r="N43" t="n">
-        <v>56801.0</v>
+        <v>56501.0</v>
       </c>
       <c r="O43" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
+        <v>86</v>
+      </c>
+      <c r="B44" t="s">
+        <v>57</v>
+      </c>
+      <c r="C44" t="n">
+        <v>569.0</v>
+      </c>
+      <c r="D44" t="s">
         <v>87</v>
       </c>
-      <c r="B44" t="s">
-        <v>47</v>
-      </c>
-      <c r="C44" t="n">
-        <v>572.0</v>
-      </c>
-      <c r="D44" t="s">
-        <v>88</v>
-      </c>
       <c r="E44" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="F44" t="n">
         <v>1.0</v>
@@ -1307,22 +1319,22 @@
         <v>88</v>
       </c>
       <c r="I44" t="n">
-        <v>2424.8</v>
+        <v>12268.1</v>
       </c>
       <c r="J44" t="n">
-        <v>147.05</v>
+        <v>3175.81</v>
       </c>
       <c r="K44" t="n">
-        <v>2277.75</v>
+        <v>9092.29</v>
       </c>
       <c r="L44" t="n">
-        <v>2277.75</v>
+        <v>9092.29</v>
       </c>
       <c r="M44" t="n">
-        <v>3.61</v>
+        <v>1.8</v>
       </c>
       <c r="N44" t="n">
-        <v>57201.0</v>
+        <v>56901.0</v>
       </c>
       <c r="O44" t="s">
         <v>88</v>
@@ -1330,66 +1342,66 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
+        <v>89</v>
+      </c>
+      <c r="B45" t="s">
+        <v>69</v>
+      </c>
+      <c r="C45" t="n">
+        <v>568.0</v>
+      </c>
+      <c r="D45" t="s">
+        <v>87</v>
+      </c>
+      <c r="E45" t="s">
+        <v>59</v>
+      </c>
+      <c r="F45" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="G45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H45" t="s">
         <v>90</v>
       </c>
-      <c r="B45" t="s">
-        <v>58</v>
-      </c>
-      <c r="C45" t="n">
-        <v>577.0</v>
-      </c>
-      <c r="D45" t="s">
-        <v>91</v>
-      </c>
-      <c r="E45" t="s">
-        <v>55</v>
-      </c>
-      <c r="F45" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="G45" t="s">
-        <v>50</v>
-      </c>
-      <c r="H45" t="s">
-        <v>92</v>
-      </c>
       <c r="I45" t="n">
-        <v>63749.58</v>
+        <v>50200.0</v>
       </c>
       <c r="J45" t="n">
-        <v>6192.12</v>
+        <v>6551.57</v>
       </c>
       <c r="K45" t="n">
-        <v>57557.46</v>
+        <v>43648.43</v>
       </c>
       <c r="L45" t="n">
-        <v>57557.46</v>
+        <v>43648.43</v>
       </c>
       <c r="M45" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="N45" t="n">
-        <v>57701.0</v>
+        <v>56801.0</v>
       </c>
       <c r="O45" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
+        <v>91</v>
+      </c>
+      <c r="B46" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" t="n">
+        <v>572.0</v>
+      </c>
+      <c r="D46" t="s">
+        <v>92</v>
+      </c>
+      <c r="E46" t="s">
         <v>93</v>
-      </c>
-      <c r="B46" t="s">
-        <v>58</v>
-      </c>
-      <c r="C46" t="n">
-        <v>582.0</v>
-      </c>
-      <c r="D46" t="s">
-        <v>56</v>
-      </c>
-      <c r="E46" t="s">
-        <v>60</v>
       </c>
       <c r="F46" t="n">
         <v>1.0</v>
@@ -1398,28 +1410,28 @@
         <v>50</v>
       </c>
       <c r="H46" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="I46" t="n">
-        <v>57600.0</v>
+        <v>2424.8</v>
       </c>
       <c r="J46" t="n">
-        <v>12914.12</v>
+        <v>147.05</v>
       </c>
       <c r="K46" t="n">
-        <v>44685.88</v>
+        <v>2277.75</v>
       </c>
       <c r="L46" t="n">
-        <v>44685.88</v>
+        <v>2277.75</v>
       </c>
       <c r="M46" t="n">
-        <v>1.91</v>
+        <v>3.61</v>
       </c>
       <c r="N46" t="n">
-        <v>58201.0</v>
+        <v>57201.0</v>
       </c>
       <c r="O46" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47">
@@ -1427,146 +1439,224 @@
         <v>94</v>
       </c>
       <c r="B47" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C47" t="n">
-        <v>581.0</v>
+        <v>577.0</v>
       </c>
       <c r="D47" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="E47" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="F47" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G47" t="s">
         <v>50</v>
       </c>
       <c r="H47" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="I47" t="n">
-        <v>19813.0</v>
+        <v>63749.58</v>
       </c>
       <c r="J47" t="n">
-        <v>2204.06</v>
+        <v>6192.12</v>
       </c>
       <c r="K47" t="n">
-        <v>17608.94</v>
+        <v>57557.46</v>
       </c>
       <c r="L47" t="n">
-        <v>17608.94</v>
+        <v>57557.46</v>
       </c>
       <c r="M47" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="N47" t="n">
-        <v>58101.0</v>
+        <v>57701.0</v>
       </c>
       <c r="O47" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B48" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="C48" t="n">
+        <v>582.0</v>
+      </c>
+      <c r="D48" t="s">
+        <v>64</v>
+      </c>
+      <c r="E48" t="s">
+        <v>54</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G48" t="s">
+        <v>50</v>
+      </c>
+      <c r="H48" t="s">
+        <v>64</v>
+      </c>
+      <c r="I48" t="n">
+        <v>57600.0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>12914.12</v>
+      </c>
+      <c r="K48" t="n">
+        <v>44685.88</v>
+      </c>
+      <c r="L48" t="n">
+        <v>44685.88</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="N48" t="n">
+        <v>58201.0</v>
+      </c>
+      <c r="O48" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>98</v>
+      </c>
+      <c r="B49" t="s">
+        <v>47</v>
+      </c>
+      <c r="C49" t="n">
+        <v>581.0</v>
+      </c>
+      <c r="D49" t="s">
+        <v>64</v>
+      </c>
+      <c r="E49" t="s">
+        <v>54</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G49" t="s">
+        <v>50</v>
+      </c>
+      <c r="H49" t="s">
+        <v>78</v>
+      </c>
+      <c r="I49" t="n">
+        <v>19813.0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2204.06</v>
+      </c>
+      <c r="K49" t="n">
+        <v>17608.94</v>
+      </c>
+      <c r="L49" t="n">
+        <v>17608.94</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N49" t="n">
+        <v>58101.0</v>
+      </c>
+      <c r="O49" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>99</v>
+      </c>
+      <c r="B50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C50" t="n">
         <v>589.0</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D50" t="s">
+        <v>100</v>
+      </c>
+      <c r="E50" t="s">
+        <v>59</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G50" t="s">
+        <v>50</v>
+      </c>
+      <c r="H50" t="s">
         <v>96</v>
       </c>
-      <c r="E48" t="s">
-        <v>49</v>
-      </c>
-      <c r="F48" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="G48" t="s">
-        <v>50</v>
-      </c>
-      <c r="H48" t="s">
-        <v>92</v>
-      </c>
-      <c r="I48" t="n">
+      <c r="I50" t="n">
         <v>11400.0</v>
       </c>
-      <c r="J48" t="n">
+      <c r="J50" t="n">
         <v>464.68</v>
       </c>
-      <c r="K48" t="n">
+      <c r="K50" t="n">
         <v>10935.32</v>
       </c>
-      <c r="L48" t="n">
+      <c r="L50" t="n">
         <v>10935.32</v>
       </c>
-      <c r="M48" t="n">
+      <c r="M50" t="n">
         <v>2.14</v>
       </c>
-      <c r="N48" t="n">
+      <c r="N50" t="n">
         <v>58901.0</v>
       </c>
-      <c r="O48" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>98</v>
+      <c r="O50" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>17</v>
+        <v>104</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>107</v>
+        <v>17</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>108</v>
@@ -1586,6 +1676,22 @@
       </c>
       <c r="B59" s="3" t="s">
         <v>112</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/carteira_mensal/Jan_2026.xlsx
+++ b/xlsx/carteira_mensal/Jan_2026.xlsx
@@ -177,7 +177,7 @@
     <t>20/12/25</t>
   </si>
   <si>
-    <t>BIANCA RODRIGUES</t>
+    <t>bianca rodrigues</t>
   </si>
   <si>
     <t>08/01/26</t>
